--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487105_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487105_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>S. LOPEZ RAMOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.462</v>
+        <v>1.6138</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.545</v>
+        <v>0.4722</v>
       </c>
       <c r="F2" t="n">
-        <v>3.007</v>
+        <v>1.1415</v>
       </c>
       <c r="G2" t="n">
-        <v>1.038</v>
+        <v>1.4726</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4047</v>
+        <v>-0.1717</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6333</v>
+        <v>1.6444</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0667</v>
+        <v>1.4459</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5936</v>
+        <v>0.0621</v>
       </c>
       <c r="L2" t="n">
-        <v>1.473</v>
+        <v>1.3838</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0287</v>
+        <v>0.0268</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.189</v>
+        <v>-0.2338</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8397</v>
+        <v>0.2606</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.9301</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.8252</v>
+        <v>-0.965</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8951</v>
+        <v>0.965</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4965</v>
+        <v>0.1411</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0701</v>
+        <v>-0.0086</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4264</v>
+        <v>0.1497</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8576</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1435</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3459</v>
+        <v>1.2951</v>
       </c>
       <c r="E3" t="n">
-        <v>2.083</v>
+        <v>-0.5073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2629</v>
+        <v>1.8024</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7138</v>
+        <v>1.038</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9387</v>
+        <v>0.4047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2249</v>
+        <v>0.6333</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2221</v>
+        <v>3.0667</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9779</v>
+        <v>1.5936</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2442</v>
+        <v>1.473</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9359</v>
+        <v>-2.0287</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9166</v>
+        <v>-1.189</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0193</v>
+        <v>-0.8397</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3511</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.158</v>
+        <v>-4.8252</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5091</v>
+        <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7087</v>
+        <v>1.3296</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7332</v>
+        <v>0.1078</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0245</v>
+        <v>1.2218</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.8576</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2859</v>
+        <v>1.1435</v>
       </c>
       <c r="X3" t="n">
         <v>-0.2859</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LOPEZ RAMOS</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8408</v>
+        <v>1.1492</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6725</v>
+        <v>0.8595</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1683</v>
+        <v>0.2896</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4726</v>
+        <v>-0.7138</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1717</v>
+        <v>-0.9387</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6444</v>
+        <v>0.2249</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4459</v>
+        <v>1.2221</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0621</v>
+        <v>0.9779</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3838</v>
+        <v>0.2442</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0268</v>
+        <v>-1.9359</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2338</v>
+        <v>-1.9166</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2606</v>
+        <v>-0.0193</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>1.3511</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-1.158</v>
       </c>
       <c r="R4" t="n">
-        <v>0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3682</v>
+        <v>0.5119</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1917</v>
+        <v>0.5097</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1765</v>
+        <v>0.0023</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2111</v>
+        <v>0.344</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.197</v>
+        <v>-0.2783</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4082</v>
+        <v>0.6223</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4092</v>
@@ -844,13 +844,13 @@
         <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0515</v>
+        <v>0.0813</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0912</v>
+        <v>-0.1725</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0396</v>
+        <v>0.2538</v>
       </c>
       <c r="V5" t="n">
         <v>0.8999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7916</v>
+        <v>-0.1045</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5192</v>
+        <v>-0.8589</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7276</v>
+        <v>0.7544</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3394</v>
@@ -922,13 +922,13 @@
         <v>1.7371</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2592</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8037</v>
+        <v>-0.1434</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4554</v>
+        <v>-0.4287</v>
       </c>
       <c r="V6" t="n">
         <v>1.228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9074</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8849</v>
+        <v>-0.7847</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0225</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6667999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>0.193</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4336</v>
+        <v>-0.2264</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DIEYE</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6721</v>
+        <v>-1.4301</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8092</v>
+        <v>0.2487</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1371</v>
+        <v>-1.6788</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1671</v>
+        <v>1.1851</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3414</v>
+        <v>-1.4603</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1742</v>
+        <v>2.6454</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6062</v>
+        <v>2.3397</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6469</v>
+        <v>-0.8591</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0407</v>
+        <v>3.1988</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5609</v>
+        <v>-1.1546</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6944</v>
+        <v>-0.6012</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1335</v>
+        <v>-0.5534</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>-0.193</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.505</v>
+        <v>0.0337</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.238</v>
+        <v>-0.1609</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.267</v>
+        <v>0.1946</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.4559</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>M. DIEYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9893</v>
+        <v>-1.572</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2302</v>
+        <v>-1.7091</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7591</v>
+        <v>0.1371</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1851</v>
+        <v>-1.1671</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4603</v>
+        <v>-1.3414</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6454</v>
+        <v>0.1742</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3397</v>
+        <v>-0.6062</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8591</v>
+        <v>-0.6469</v>
       </c>
       <c r="L9" t="n">
-        <v>3.1988</v>
+        <v>0.0407</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1546</v>
+        <v>-0.5609</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6012</v>
+        <v>-0.6944</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5534</v>
+        <v>0.1335</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5255</v>
+        <v>-0.4049</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6398</v>
+        <v>-0.1378</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1143</v>
+        <v>-0.267</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4559</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6581</v>
+        <v>-2.5113</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8744</v>
+        <v>-2.915</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2163</v>
+        <v>0.4037</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1838</v>
@@ -1234,13 +1234,13 @@
         <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1884</v>
+        <v>-0.0416</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2208</v>
+        <v>0.1801</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4092</v>
+        <v>-0.2218</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2859</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2933</v>
+        <v>-2.6676</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4172</v>
+        <v>-2.979</v>
       </c>
       <c r="F11" t="n">
-        <v>0.124</v>
+        <v>0.3113</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6766</v>
@@ -1312,13 +1312,13 @@
         <v>2.8951</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7674</v>
+        <v>-0.1418</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.419</v>
+        <v>0.0192</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3484</v>
+        <v>-0.161</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6562</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0236</v>
+        <v>-4.702</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.5369</v>
+        <v>-4.6168</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4868</v>
+        <v>-0.0852</v>
       </c>
       <c r="G12" t="n">
         <v>-4.4919</v>
@@ -1390,13 +1390,13 @@
         <v>2.5091</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5897</v>
+        <v>-0.268</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9227</v>
+        <v>-0.0026</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6669</v>
+        <v>-0.2654</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3281</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.4756</v>
+        <v>-9.285500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.2585</v>
+        <v>-13.0687</v>
       </c>
       <c r="F13" t="n">
-        <v>3.783</v>
+        <v>3.782900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-9.9529</v>
@@ -1468,13 +1468,13 @@
         <v>19.3007</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7468999999999996</v>
+        <v>0.4427999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1366</v>
+        <v>0.0532000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3896999999999997</v>
+        <v>0.3897</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7406000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2198</v>
+        <v>5.9138</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9552</v>
+        <v>1.9538</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2646</v>
+        <v>3.96</v>
       </c>
       <c r="G14" t="n">
         <v>3.5309</v>
@@ -1546,13 +1546,13 @@
         <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1448</v>
+        <v>0.8388</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2586</v>
+        <v>0.2572</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1137</v>
+        <v>0.5816</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1792</v>
+        <v>4.7523</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2853</v>
+        <v>1.8862</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8938</v>
+        <v>2.8661</v>
       </c>
       <c r="G15" t="n">
         <v>5.8381</v>
@@ -1624,13 +1624,13 @@
         <v>2.7021</v>
       </c>
       <c r="S15" t="n">
-        <v>0.148</v>
+        <v>0.7211</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9822</v>
+        <v>-0.3814</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1302</v>
+        <v>1.1025</v>
       </c>
       <c r="V15" t="n">
         <v>-1.228</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.364</v>
+        <v>3.1114</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1505</v>
+        <v>1.2791</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7864</v>
+        <v>1.8323</v>
       </c>
       <c r="G16" t="n">
-        <v>1.767</v>
+        <v>0.068</v>
       </c>
       <c r="H16" t="n">
-        <v>1.832</v>
+        <v>1.5411</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.065</v>
+        <v>-1.473</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4551</v>
+        <v>1.148</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1527</v>
+        <v>1.1073</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3024</v>
+        <v>0.0407</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6881</v>
+        <v>-1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3207</v>
+        <v>0.4338</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3674</v>
+        <v>-1.5137</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9301</v>
+        <v>2.5091</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2809</v>
+        <v>-0.0145</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6954</v>
+        <v>-0.4177</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4145</v>
+        <v>0.4032</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.614</v>
+        <v>1.5138</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8985</v>
+        <v>2.7969</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8784999999999999</v>
+        <v>3.4495</v>
       </c>
       <c r="F17" t="n">
-        <v>2.02</v>
+        <v>-0.6526</v>
       </c>
       <c r="G17" t="n">
-        <v>0.068</v>
+        <v>1.767</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5411</v>
+        <v>1.832</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.473</v>
+        <v>-0.065</v>
       </c>
       <c r="J17" t="n">
-        <v>1.148</v>
+        <v>3.4551</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1073</v>
+        <v>2.1527</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0407</v>
+        <v>1.3024</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.08</v>
+        <v>-1.6881</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4338</v>
+        <v>-0.3207</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5137</v>
+        <v>-1.3674</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5091</v>
+        <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2274</v>
+        <v>-0.2862</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8183</v>
+        <v>-0.0056</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5909</v>
+        <v>-0.2806</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5138</v>
+        <v>-0.614</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8952</v>
+        <v>1.8305</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5809</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3144</v>
+        <v>0.8491</v>
       </c>
       <c r="G18" t="n">
         <v>1.9875</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0536</v>
+        <v>-0.1183</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4468</v>
+        <v>-0.0462</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6068</v>
+        <v>-0.0721</v>
       </c>
       <c r="V18" t="n">
         <v>1.3125</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DE LARREA ASENJO</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1584</v>
+        <v>0.5784</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1962</v>
+        <v>-3.3965</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0378</v>
+        <v>3.975</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7017</v>
+        <v>-0.5928</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4347</v>
+        <v>-0.1615</v>
       </c>
       <c r="I19" t="n">
-        <v>0.267</v>
+        <v>-0.4313</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6417</v>
+        <v>-2.0154</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6417</v>
+        <v>-0.8023</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.2131</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06</v>
+        <v>1.4226</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.207</v>
+        <v>0.6408</v>
       </c>
       <c r="O19" t="n">
-        <v>0.267</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.386</v>
+        <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1573</v>
+        <v>0.6501</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0595</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0978</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>M. DE LARREA ASENJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2964</v>
+        <v>0.4456</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8973</v>
+        <v>0.2963</v>
       </c>
       <c r="F20" t="n">
-        <v>3.6009</v>
+        <v>0.1493</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5928</v>
+        <v>0.7017</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1615</v>
+        <v>0.4347</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4313</v>
+        <v>0.267</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.0154</v>
+        <v>0.6417</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8023</v>
+        <v>0.6417</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2131</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4226</v>
+        <v>0.06</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6408</v>
+        <v>-0.207</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.267</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>-0.386</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1231</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2247</v>
+        <v>0.1299</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5658</v>
+        <v>0.0407</v>
       </c>
       <c r="U20" t="n">
-        <v>0.341</v>
+        <v>0.0892</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8197</v>
+        <v>-0.5325</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7819</v>
+        <v>-0.6818</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0378</v>
+        <v>0.1493</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2764</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1573</v>
+        <v>0.1299</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0595</v>
+        <v>0.0407</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0978</v>
+        <v>0.0892</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2254</v>
+        <v>-0.9716</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8618</v>
+        <v>-0.6615</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3636</v>
+        <v>-0.3101</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6081</v>
@@ -2170,13 +2170,13 @@
         <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.3635</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2829</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3345</v>
+        <v>-0.2809</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3445</v>
+        <v>-2.6849</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7548</v>
+        <v>-4.2555</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4104</v>
+        <v>1.5706</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5454</v>
@@ -2248,13 +2248,13 @@
         <v>2.5091</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.2115</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5315</v>
+        <v>0.0308</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0205</v>
+        <v>0.1807</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5537</v>
+        <v>-2.7616</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5337</v>
+        <v>-4.6338</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9799</v>
+        <v>1.8722</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9177999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>1.158</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0589</v>
+        <v>0.851</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3398</v>
+        <v>0.2396</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7191</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5717</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.4754</v>
+        <v>12.4783</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.782899999999998</v>
+        <v>-3.782799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>14.2584</v>
+        <v>16.2612</v>
       </c>
       <c r="G25" t="n">
         <v>9.9527</v>
@@ -2404,13 +2404,13 @@
         <v>18.3357</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7467999999999996</v>
+        <v>2.7498</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3896999999999999</v>
+        <v>-0.3896000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1366</v>
+        <v>3.1394</v>
       </c>
       <c r="V25" t="n">
         <v>0.7407000000000002</v>
